--- a/data/curtailment/unidades_geradoras.xlsx
+++ b/data/curtailment/unidades_geradoras.xlsx
@@ -2731,7 +2731,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>EQTL (Echo)</t>
+          <t>Equatorial</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Voltália</t>
+          <t>Voltalia</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Voltália</t>
+          <t>Voltalia</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Voltália</t>
+          <t>Voltalia</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Voltália</t>
+          <t>Voltalia</t>
         </is>
       </c>
     </row>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>EQTL (Echo)</t>
+          <t>Equatorial</t>
         </is>
       </c>
     </row>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>EQTL (Echo)</t>
+          <t>Equatorial</t>
         </is>
       </c>
     </row>
@@ -4206,7 +4206,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Voltália</t>
+          <t>Voltalia</t>
         </is>
       </c>
     </row>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>EQTL (Echo)</t>
+          <t>Equatorial</t>
         </is>
       </c>
     </row>
@@ -4681,7 +4681,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>CGN Brazil</t>
+          <t>CGN Brasil</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>CGN Brazil</t>
+          <t>CGN Brasil</t>
         </is>
       </c>
     </row>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>CGN Brazil</t>
+          <t>CGN Brasil</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>EQTL (Echo)</t>
+          <t>Equatorial</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>CGN Brazil</t>
+          <t>CGN Brasil</t>
         </is>
       </c>
     </row>
@@ -5706,7 +5706,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>CGN Brazil</t>
+          <t>CGN Brasil</t>
         </is>
       </c>
     </row>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Voltália</t>
+          <t>Voltalia</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>EQTL (Echo)</t>
+          <t>Equatorial</t>
         </is>
       </c>
     </row>
@@ -6756,7 +6756,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>EQTL (Echo)</t>
+          <t>Equatorial</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>EQTL (Echo)</t>
+          <t>Equatorial</t>
         </is>
       </c>
     </row>

--- a/data/curtailment/unidades_geradoras.xlsx
+++ b/data/curtailment/unidades_geradoras.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Solar" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eólica" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Solar" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Eólica" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>EQTL (Echo)</t>
+          <t>Equatorial</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Essentia (Pátria)</t>
+          <t>Essentia</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ibitu Energia</t>
+          <t>Ibitu</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Qair Brasil</t>
+          <t>Qair</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>EQTL (Echo)</t>
+          <t>Equatorial</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>EQTL (Echo)</t>
+          <t>Equatorial</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Qair Brasil</t>
+          <t>Qair</t>
         </is>
       </c>
     </row>
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Essentia Energia</t>
+          <t>Essentia</t>
         </is>
       </c>
     </row>

--- a/data/curtailment/unidades_geradoras.xlsx
+++ b/data/curtailment/unidades_geradoras.xlsx
@@ -2290,7 +2290,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Equatorial</t>
+          <t>Other</t>
         </is>
       </c>
     </row>

--- a/data/curtailment/unidades_geradoras.xlsx
+++ b/data/curtailment/unidades_geradoras.xlsx
@@ -655,7 +655,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ribeiro Goncalves</t>
+          <t>Ribeiro Gonçalves</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
